--- a/artfynd/A 6154-2026 artfynd.xlsx
+++ b/artfynd/A 6154-2026 artfynd.xlsx
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448214</v>
+        <v>131448226</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386220</v>
+        <v>386338</v>
       </c>
       <c r="R5" t="n">
-        <v>6758075</v>
+        <v>6757999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448226</v>
+        <v>131448214</v>
       </c>
       <c r="B6" t="n">
         <v>79249</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386338</v>
+        <v>386220</v>
       </c>
       <c r="R6" t="n">
-        <v>6757999</v>
+        <v>6758075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 6154-2026 artfynd.xlsx
+++ b/artfynd/A 6154-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>131448216</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448229</v>
       </c>
       <c r="B4" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448226</v>
+        <v>131448214</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386338</v>
+        <v>386220</v>
       </c>
       <c r="R5" t="n">
-        <v>6757999</v>
+        <v>6758075</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448214</v>
+        <v>131448226</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386220</v>
+        <v>386338</v>
       </c>
       <c r="R6" t="n">
-        <v>6758075</v>
+        <v>6757999</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,7 +1218,7 @@
         <v>131448211</v>
       </c>
       <c r="B7" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131448219</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131448220</v>
       </c>
       <c r="B9" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131448227</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>131448218</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>131448230</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 6154-2026 artfynd.xlsx
+++ b/artfynd/A 6154-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448231</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131448216</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448229</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131448214</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>131448226</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131448211</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131448219</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131448220</v>
       </c>
       <c r="B9" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>131448227</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>131448218</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>131448230</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 6154-2026 artfynd.xlsx
+++ b/artfynd/A 6154-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448231</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131448216</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131448229</v>
       </c>
       <c r="B4" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>131448214</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>131448226</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131448211</v>
       </c>
       <c r="B7" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131448219</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448220</v>
+        <v>131448227</v>
       </c>
       <c r="B9" t="n">
-        <v>78919</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386217</v>
+        <v>386336</v>
       </c>
       <c r="R9" t="n">
-        <v>6758038</v>
+        <v>6758002</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448227</v>
+        <v>131448220</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>78920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386336</v>
+        <v>386217</v>
       </c>
       <c r="R10" t="n">
-        <v>6758002</v>
+        <v>6758038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448218</v>
+        <v>131448230</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386148</v>
+        <v>386424</v>
       </c>
       <c r="R11" t="n">
-        <v>6758017</v>
+        <v>6757997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448230</v>
+        <v>131448218</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386424</v>
+        <v>386148</v>
       </c>
       <c r="R12" t="n">
-        <v>6757997</v>
+        <v>6758017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 6154-2026 artfynd.xlsx
+++ b/artfynd/A 6154-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131448231</v>
+        <v>131448220</v>
       </c>
       <c r="B2" t="n">
-        <v>57100</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386425</v>
+        <v>386217</v>
       </c>
       <c r="R2" t="n">
-        <v>6758026</v>
+        <v>6758038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448216</v>
+        <v>131448228</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386205</v>
+        <v>386322</v>
       </c>
       <c r="R3" t="n">
-        <v>6758052</v>
+        <v>6758001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448229</v>
+        <v>131448214</v>
       </c>
       <c r="B4" t="n">
-        <v>79893</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386342</v>
+        <v>386220</v>
       </c>
       <c r="R4" t="n">
-        <v>6758000</v>
+        <v>6758075</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448214</v>
+        <v>131448216</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386220</v>
+        <v>386205</v>
       </c>
       <c r="R5" t="n">
-        <v>6758075</v>
+        <v>6758052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448226</v>
+        <v>131448218</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386338</v>
+        <v>386148</v>
       </c>
       <c r="R6" t="n">
-        <v>6757999</v>
+        <v>6758017</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131448211</v>
+        <v>131448219</v>
       </c>
       <c r="B7" t="n">
-        <v>79893</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386215</v>
+        <v>386230</v>
       </c>
       <c r="R7" t="n">
-        <v>6758072</v>
+        <v>6758036</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448219</v>
+        <v>131448225</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386230</v>
+        <v>386285</v>
       </c>
       <c r="R8" t="n">
-        <v>6758036</v>
+        <v>6758011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448220</v>
+        <v>131448226</v>
       </c>
       <c r="B9" t="n">
-        <v>78940</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386217</v>
+        <v>386338</v>
       </c>
       <c r="R9" t="n">
-        <v>6758038</v>
+        <v>6757999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,11 +1534,11 @@
         <v>131448227</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1643,14 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448218</v>
+        <v>131448230</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386148</v>
+        <v>386424</v>
       </c>
       <c r="R11" t="n">
-        <v>6758017</v>
+        <v>6757997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448230</v>
+        <v>131448224</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386424</v>
+        <v>386301</v>
       </c>
       <c r="R12" t="n">
-        <v>6757997</v>
+        <v>6758006</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,6 +1849,444 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131448211</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>386215</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6758072</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131448229</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>386342</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6758000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131448223</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>386311</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6758002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131448231</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>386425</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6758026</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
